--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -1137,9 +1137,9 @@
         <is>
           <t>Auth: Unauthenticated; no APP_KEY required.
 Affected version: Laravel Framework through 8.70.2 (&lt;= 8.70.2)
-Config: Upload endpoint accepts a file with no effective validation of executable types and stores it under its original client filename in a web-served, PHP-executing directory; an uploaded .php therefore lands in the docroot and runs. (NVD root cause: a mimes/mimetypes allowlist that omits executable extensions such as .phar, which Apache+mod_php still executes.)
+Config: Upload endpoint validates uploads with the framework `mimes:jpg,jpeg,png,gif` rule and stores accepted files under their original client filename in a web-served, .phar-executing directory. NVD root cause: on laravel/framework &lt;= 8.70.2, validateMimes()-&gt;shouldBlockPhpUpload() blocks php/php3/php4/php5/phtml but omits `.phar`, so a GIF-polyglot .phar (guessExtension()=='gif') passes the image validation, is stored under its .phar name, and executes where Apache/Debian maps .phar -&gt; application/x-httpd-php.
 Network: Attacker must reach the HTTP(S) upload endpoint and then request the web-served uploaded file path for proof. No separate callback, listener, or OOB channel is required.
-Lab rebuild: `bash vuln-labs/framework/laravel/11.x/cve-2021-43617_upload-rce_39004-40004/run.sh`; module `modules/cves/cve_2021_43617.py`; minimal app-owned upload harness with deliberate no-validation storage into a web-served PHP-executing path; the entrypoint injects `validateCsrfTokens(except: ['/upload'])` into bootstrap/app.php so the tokenless unauthenticated POST is accepted (CSRF exemption is harness route-wiring, not authentication); not a package-version proof; php:8.2-apache; vulnerable/hardened HTTP ports 39004/40004.
+Lab rebuild: `bash vuln-labs/framework/laravel/8.70.2/cve-2021-43617_upload-rce_39004-40004/run.sh`; module `modules/cves/cve_2021_43617.py`; FAITHFUL: runs laravel/framework 8.70.2 (last affected) on php:8.0-apache; the /upload route validates with the real framework `mimes:jpg,jpeg,png,gif` rule, which in 8.70.2 (validateMimes -&gt; shouldBlockPhpUpload) fails to block `.phar`; a GIF-polyglot .phar (guessExtension()=='gif') passes validation, is stored under its original name, and executes via the Apache .phar handler; an L8 App\Http\Middleware\VerifyCsrfToken excepts /upload (harness route-wiring, not authentication); hardened twin adds phar to the blocklist (the real 8.70.3+ fix -&gt; 422); vulnerable/hardened HTTP ports 39004/40004.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: Yes

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -3409,7 +3409,7 @@
 Affected version: Laravel &lt;= 5.5.40 or 5.6.x &lt;= 5.6.29 (affected range)
 Config: Old app images / committed .env shipping default or leaked APP_KEY enable the unauthenticated path (with a valid APP_KEY, an encrypted serialized gadget in X-XSRF-TOKEN executes via Encrypter::decrypt() -&gt; unserialize())
 Network: Attacker must reach the HTTP(S) Laravel endpoint that decrypts X-XSRF-TOKEN/cookie payloads. Exploitation requires a valid APP_KEY to forge the encrypted serialized gadget; proof is direct HTTP sink/readback, not OOB.
-Lab rebuild: `bash vuln-labs/framework/laravel/5.6.x/cve-2018-15133_xsrf-deserialize-rce_39002-40002/run.sh`; module `modules/cves/cve_2018_15133.py`; minimal framework/app-sink harness with a lab X-XSRF-TOKEN decrypt route, phpggc, and fixed lab APP_KEY `base64:AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA=`; not a pinned stock vulnerable full app; php:7.2-apache; vulnerable/hardened HTTP ports 39002/40002.
+Lab rebuild: `bash vuln-labs/framework/laravel/5.6.x/cve-2018-15133_xsrf-deserialize-rce_39002-40002/run.sh`; module `modules/cves/cve_2018_15133.py`; Laravel 5.6.29 on php:7.2-apache with a REAL random APP_KEY (php artisan key:generate) leaked via a web-reachable /.env (Alias) — the scanner recovers the real key from the leak (no --app-key needed), then forges the encrypted X-XSRF-TOKEN phpggc gadget at the decrypt sink; the X-XSRF-TOKEN decrypt route is a lab-provided app sink (the framework ships no such HTTP route). vulnerable/hardened HTTP ports 39002/40002.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: Yes

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -2343,7 +2343,7 @@
 Affected version: laravel/reverb &lt;= 1.6.3 (fixed 1.7.0 with an allow-list).
 Config: In production, the Redis horizontal-scaling backend must be enabled (REVERB_SCALING_ENABLED=true) so a Reverb worker subscribes to the Redis scaling channel. This lab models that end state directly: its worker subscribes to the 'reverb' channel unconditionally in BOTH the vulnerable and hardened profiles (no REVERB_SCALING_ENABLED env gate is read; compose sets only APP_URL, LAB_HARDENED, REDIS_HOST, REDIS_PORT), so an active scaling subscriber is always present and there is no config gate to satisfy.
 Network: Exploitation is OOB/side-channel, not an HTTP route exploit. Attacker must be able to publish a crafted serialized message to the Redis scaling bus (local lab: redis on host 127.0.0.1:6379 vulnerable / :6380 hardened, or operator-supplied redis_host/redis_port). HTTP 37002/38002 fingerprints Reverb and polls optional /reverb-oob readback; the RCE trigger is Redis Pub/Sub consumption by the worker.
-Lab rebuild: `bash vuln-labs/first-party/reverb/1.6.3/cve-2026-23524_redis-scaling-deserialize-rce_37002-38002/run.sh`; module `modules/cves/cve_2026_23524.py`; minimal Reverb behavior harness with Redis scaling deserialize path; HTTP readback ports 37002/38002 and Redis Pub/Sub ports 6379 vulnerable / 6380 hardened; php:8.2-apache plus redis:7-alpine.
+Lab rebuild: `bash vuln-labs/first-party/reverb/1.6.3/cve-2026-23524_redis-scaling-deserialize-rce_37002-38002/run.sh`; module `modules/cves/cve_2026_23524.py`; FAITHFUL: real Laravel 11 app running the genuine vulnerable laravel/reverb 1.6.3 via `php artisan reverb:start` with REVERB_SCALING_ENABLED=true, subscribed to Redis pub/sub channel 'reverb'. The real PusherPubSubIncomingMessageHandler::handle() runs unserialize() (no allowed_classes) on each message's 'application' field; publishing {"application":"&lt;real phpggc laravel/rce9 gadget&gt;"} to Redis detonates in the Reverb worker (root RCE), proven out-of-band via a /reverb-oob callback collector. Hardened twin runs reverb 1.7.0 (the allowed_classes fix) -&gt; gadget neutralized. HTTP 37002/38002; Redis 6379 vuln / 6380 hardened; php:8.2-apache + redis:7-alpine.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: Yes

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -869,7 +869,7 @@
 Affected version: Vulnerable framework Laravel/laravel-framework &lt;= 8.5.9 installed to provide the PendingBroadcast::__destruct() POP gadget
 Config: Target application exposes a reachable unserialize() sink on attacker-controlled data…
 Network: Attacker must reach a developer-provided HTTP(S) endpoint that passes attacker-controlled input to unserialize(). The gadget trigger and proof are in-band HTTP; no callback or OOB channel is required.
-Lab rebuild: `bash vuln-labs/framework/laravel/8.5.9/cve-2021-28254_pendingbroadcast-deser_39008-40008/run.sh`; module `modules/cves/cve_2021_28254.py`; minimal gadget/app-sink harness for the PendingBroadcast POP chain with an intentionally reachable unserialize sink; not a stock exact-version app; php:7.4-apache; vulnerable/hardened HTTP ports 39008/40008.
+Lab rebuild: `bash vuln-labs/framework/laravel/8.5.9/cve-2021-28254_pendingbroadcast-deser_39008-40008/run.sh`; module `modules/cves/cve_2021_28254.py`; minimal gadget/app-sink harness for the PendingBroadcast POP chain with an intentionally reachable unserialize sink; not a stock exact-version app; php:7.4-apache; vulnerable/hardened HTTP ports 39008/40008. NOTE: the /deserialize unserialize sink is INHERENT to this CVE — CVE-2021-28254 is a laravel/framework POP gadget chain that only fires when the APPLICATION calls unserialize() on attacker input; the framework exposes no such HTTP sink itself. The gadget is a genuine phpggc PendingBroadcast chain (real, not fabricated), so this is faithful for the bug class; the lab-supplied app sink is a necessary condition of the vulnerability, not a shortcut.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: Yes
@@ -2476,7 +2476,7 @@
 Affected version: Laravel framework &lt; 5.8.17 (upstream framework fix adds escapeshellarg() to both link() arguments; ref commit 44c3feb604944599ad1c782a9942981c3991fa31). NOTE: this affected-version field describes the historical framework CVE; the reproducible labs do NOT pin &lt; 5.8.17 — they re-create the command-injection CLASS (see Config) and the detector/exploit are version-agnostic, keying on reflected shell output rather than a version banner.
 Config: The DEFAULT reproducible lab (ports 39000/40000, what run.sh builds and the module exploit() proves against) models the command-injection class on LINUX: a public GET /storage/link route concatenates the attacker-controlled `target`/`link` query params straight into a shell `ln -s &lt;target&gt; &lt;link&gt; 2&gt;&amp;1` via shell_exec on php:8.2-apache, with no escaping, and reflects the combined stdout+stderr. The original CVE's `mklink` Windows-only framework branch is reproduced only by the OPTIONAL Windows sub-lab (raw PHP 7.3.33 + router.php running `cmd.exe /C mklink`), which requires Docker in Windows containers mode. The lab's hardened twin does NOT add escapeshellarg(); it replaces the shell invocation with PHP's native symlink() plus an allowlist that rejects shell metacharacters and '..' traversal and returns a fixed sanitized status (no reflected OS output) — same approach on the Windows hardened path.
 Network: Attacker must reach the HTTP(S) route that invokes the vulnerable storage-link sink. The command sink is local shell execution with a direct HTTP trigger/proof (Linux `ln -s` in the default lab, Windows `mklink` in the optional sub-lab); no callback or OOB channel is required.
-Lab rebuild: Linux minimal app-owned command harness `bash vuln-labs/framework/laravel/11.x/cve-2020-19316_filesystem-link-cmdi_39000-40000/run.sh`; Windows command-path harness `powershell -ExecutionPolicy Bypass -File vuln-labs/framework/laravel/11.x/cve-2020-19316_filesystem-link-cmdi_39000-40000/windows/run.ps1` or `windows/run.bat`; module `modules/cves/cve_2020_19316.py`; Linux proof is a custom link-command route, while true `mklink` proof requires Docker in Windows containers mode; vulnerable/hardened HTTP ports 39000/40000.
+Lab rebuild: Linux minimal app-owned command harness `bash vuln-labs/framework/laravel/11.x/cve-2020-19316_filesystem-link-cmdi_39000-40000/run.sh`; Windows command-path harness `powershell -ExecutionPolicy Bypass -File vuln-labs/framework/laravel/11.x/cve-2020-19316_filesystem-link-cmdi_39000-40000/windows/run.ps1` or `windows/run.bat`; module `modules/cves/cve_2020_19316.py`; Linux proof is a custom link-command route, while true `mklink` proof requires Docker in Windows containers mode; vulnerable/hardened HTTP ports 39000/40000. HONESTY/LIMITATION: CVE-2020-19316 is a WINDOWS-ONLY `mklink` command injection in Filesystem::link() (&lt;5.8.17). The Linux twin is a command-injection-CLASS harness (a lab route running `ln` via shell) — NOT the real framework code path; the real CVE is not reproducible on this Linux Docker host. Faithful mklink proof needs Windows containers (the windows/ harness).
 Flags:
 - Requires Auth (detect): No
 - Command Capable: Yes
@@ -3946,7 +3946,7 @@
 Mechanism: CVE-2020-24940 is Eloquent table-name stripping, NOT a generic over-post or a $guarded bypass. On Laravel &lt; 6.18.34 / &lt; 7.23.2, Model::fill()'s removeTableFromKey() strips a table prefix from a mass-assignment key (`users.is_admin` -&gt; `is_admin`) BEFORE the fillable/guarded check; fixed in 6.18.34 / 7.23.2 (stops stripping + isFillable() rejects any key containing '.').
 Config: The application defends a sensitive column with an APPLICATION-LAYER bare-name input filter (lab: app_filter() unsets a plain `is_admin` key before Model::create()). The exploit defeats that filter via a TABLE-QUALIFIED key `users.is_admin`: the bare-name filter does not match it, and the vulnerable framework then strips `users.` and writes is_admin=1. This is table-name stripping defeating the app filter; it is NOT an Eloquent $guarded bypass (a dotted key cannot reach a $guarded column on either version).
 Network: Attacker must reach the HTTP(S) mass-assignment route that feeds request input into create()/update()/fill()/save(). Proof is a direct in-band privilege-field write (is_admin read back true), with a control showing the bare `is_admin` key is blocked. No callback or OOB channel.
-Lab rebuild: `bash vuln-labs/framework/laravel/6.x/cve-2020-24940_mass-assignment_39007-40007/run.sh`; module `modules/cves/cve_2020_24940.py`; the VULNERABLE profile pins Laravel 6.18.33 (last affected) and the HARDENED twin pins 6.18.34 (the genuine upstream fix) via the LARAVEL_FRAMEWORK_VERSION build-arg; same app code on both (a POST /register whose app_filter() blocks the bare `is_admin` key) so the only differentiator is the real framework version; php:7.4-apache; vulnerable/hardened HTTP ports 39007/40007. mitigate.sh applies the genuine 6.18.34 upgrade in-place (revert downgrades to 6.18.33).
+Lab rebuild: `bash vuln-labs/framework/laravel/6.x/cve-2020-24940_mass-assignment_39007-40007/run.sh`; module `modules/cves/cve_2020_24940.py`; the VULNERABLE profile pins Laravel 6.18.33 (last affected) and the HARDENED twin pins 6.18.34 (the genuine upstream fix) via the LARAVEL_FRAMEWORK_VERSION build-arg; same app code on both (a POST /register whose app_filter() blocks the bare `is_admin` key) so the only differentiator is the real framework version; php:7.4-apache; vulnerable/hardened HTTP ports 39007/40007. mitigate.sh applies the genuine 6.18.34 upgrade in-place (revert downgrades to 6.18.33). HONESTY/LIMITATION: the 'privilege escalation' impact depends on the lab's app_filter() strawman (it blacklists only the bare key); at the framework level the table-prefix strip is an over-post/data-integrity issue, and (as with CVE-2020-24941, verified empirically) a dotted/prefixed key does NOT reach a $guarded column. Treat as a mass-assignment behavior demo, not a proven guarded bypass.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: No
@@ -4078,7 +4078,7 @@
 Affected version: Laravel before 6.18.35 or 7.x before 7.24.0 (laravel/framework; patched in 6.18.35 and 7.24.0)
 Config: Eloquent model uses the $guarded property (NOT $fillable, which is immune and Laravel-recommended) AND lists individual columns
 Network: Attacker must reach a developer-provided HTTP(S) mass-assignment sink on a model using guarded JSON-path attributes. Proof is direct in-band state change; no callback or OOB channel is required.
-Lab rebuild: `bash vuln-labs/framework/laravel/6.18.34/cve-2020-24941_guarded-mass-assignment_39009-40009/run.sh`; module `modules/cves/cve_2020_24941.py`; Laravel model uses guarded JSON/nested attributes with a reachable mass-assignment sink; php:7.4-apache; vulnerable/hardened HTTP ports 39009/40009.
+Lab rebuild: `bash vuln-labs/framework/laravel/6.18.34/cve-2020-24941_guarded-mass-assignment_39009-40009/run.sh`; module `modules/cves/cve_2020_24941.py`; Laravel 6.18.34 model with $guarded=['id','is_admin'] and a reachable Setting::create($request-&gt;all()) sink; php:7.4-apache; ports 39009/40009. HONESTY/LIMITATION: empirically the framework guard HOLDS on 6.18.34 — JSON-path (is_admin-&gt;x), nested (is_admin-&gt;a-&gt;b), and table-prefix (settings.is_admin) keys all leave is_admin=false. The advisory's guarded-column bypass is NOT reproducible here; the demonstrated write lands only in a NON-guarded JSON column (data-&gt;marker) = benign over-post / data-integrity, NOT privilege escalation. Reported as detection of the mass-assignment surface, not a proven guarded bypass.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: No

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -2203,10 +2203,10 @@
       </c>
       <c r="N13" s="23" t="inlineStr">
         <is>
-          <t>Auth: Unauthenticated by CVE class, and the deployed lab matches it — the vulnerable sink (untyped `public $name` on App\Livewire\PublicDemo) is mounted on the PUBLIC `/demo` route with web middleware only (no auth), so the RCE is reachable with NO credentials. Seeded creds are OPTIONAL (only for the authenticated PersonalAccessTokens fallback path); no APP_KEY required.
+          <t>Auth: AUTHENTICATED against this lab. The lab now exploits the REAL stock Snipe-IT sink — the untyped `public $name` on App\Livewire\PersonalAccessTokens at the authenticated route /account/api (the synthetic unauthenticated /demo component was removed for realism). Detection runs unauthenticated (finds no reachable component -&gt; not_detected); exploitation requires seeded staff creds (-U admin -P Password123!). The Livewire hydration bug is unauthenticated by CVE class, but the genuine Snipe-IT surface is auth-gated. No APP_KEY required.
 Affected version: Reachable Livewire v3 component, versions 3.0.0-beta.1 through 3.6.3 (fixed in 3.6.4)
 Config: Component has at least one untyped/weakly-typed public property (e.g. public $count = 0;); a scalar type hint such as public int $count closes the hole
-Network: Attacker must reach the vulnerable Livewire component/update HTTP(S) endpoint. The lab exposes this unauthenticated at /demo (web middleware only); the scanner probes the public surface first and only uses seeded auth if credentials are supplied. The exploit trigger and proof are in-band HTTP, not OOB.
+Network: Attacker must authenticate to Snipe-IT and reach the real Livewire component at /account/api (the module logs in with -U/-P, fetches the component snapshot, and sends the malicious hydration update). The exploit trigger and proof are in-band HTTP, not OOB.
 Lab rebuild: `bash vuln-labs/apps/snipe-it/8.1.18/cve-2025-54068_auth-deserialize-rce_41004-42004/run.sh`; module `modules/cves/cve_2025_54068.py`; Snipe-IT 8.1.18 with vulnerable Livewire v3 component on php:8.2-apache; seeded admin `admin` / `Password123!` (optional, for the authed fallback path); vulnerable/hardened HTTP ports 41004/42004.
 Flags:
 - Requires Auth (detect): No

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:Y31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="16.38" customWidth="1" style="22" min="1" max="1"/>
@@ -4537,6 +4537,88 @@
         </is>
       </c>
       <c r="Y30" s="23" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>CVE-2016-10074</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>Dependency upgrade</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>SwiftMailer (mail transport bundled by legacy Laravel 4.x/5.0) — NOT Laravel core</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="inlineStr">
+        <is>
+          <t>[SwiftMailer package CVE (&lt;5.4.5), NOT Laravel core. Needs old Laravel with sendmail transport plus attacker-controlled From. No lab present.] SwiftMailer sendmail argument-injection RCE</t>
+        </is>
+      </c>
+      <c r="N31" s="0" t="inlineStr">
+        <is>
+          <t>Auth: Unauthenticated; no APP_KEY required.
+Affected version: SwiftMailer &lt;= 5.4.4 when Laravel or another PHP app uses the vulnerable sendmail/mail transport.
+Config: A reachable mail-sending endpoint passes attacker-controlled From/Sender/Return-Path data into SwiftMailer sendmail transport.
+Network: Attacker must reach the HTTP(S) mail-send proof endpoint. Exploitation injects sendmail arguments through the email reverse-path and reads the written proof file over HTTP; no APP_KEY, callback, or external OOB channel is required.
+Flags:
+- Requires Auth (detect): No
+- Command Capable: Yes
+- APP_KEY Required: No</t>
+        </is>
+      </c>
+      <c r="P31" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q31" s="0" t="inlineStr">
+        <is>
+          <t>No dedicated lab (SwiftMailer package CVE; not reproducible against stock Laravel)</t>
+        </is>
+      </c>
+      <c r="R31" s="0" t="inlineStr">
+        <is>
+          <t>modules/cves/cve_2016_10074.py</t>
+        </is>
+      </c>
+      <c r="S31" s="0" t="inlineStr">
+        <is>
+          <t>modules/cves/cve_2016_10074.py</t>
+        </is>
+      </c>
+      <c r="T31" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U31" s="0" t="inlineStr">
+        <is>
+          <t>No dedicated lab; not run</t>
+        </is>
+      </c>
+      <c r="Y31" s="0" t="inlineStr">
+        <is>
+          <t>Added for completeness: ships in check.py --list but was absent from the sheet. SwiftMailer &lt;5.4.5 sendmail arg-injection RCE; requires old Laravel with the sendmail/mail transport + attacker-controlled From. Reclassified swiftmailer_dependency_rce.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="11">

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>Auth: Unauthenticated; the lab exposes a public Livewire upload component at /upload. No APP_KEY or credentials are required.
+          <t>Auth: Advisory rates this PR:L — a real deployment requires an AUTHENTICATED low-privilege user able to reach a Livewire upload component. The lab mounts the component on a PUBLIC /upload route (no auth) for reproduction, so the scanner needs no credentials here, but production exploitation is not truly anonymous. No APP_KEY required.
 Affected version: Livewire &lt; 2.12.7 or v3 &lt; 3.5.2 (v3 affected range v3.0.0-beta.1 through v3.5.1; fixed in 2.12.7 and 3.5.2)
 Config: Application stores uploads using the original client filename (e.g. $file-&gt;getClientOriginalName() / storeAs() preserving the client name) rather than Livewire's default randomized hashed filename
 Network: Attacker must reach the Livewire upload HTTP(S) endpoint and then request the web-served uploaded file path for proof. The primary unauthenticated /upload path needs no credentials; seeded credentials (admin@example.com / Password123!) are only for the secondary authenticated Filament logo-upload sink. No callback or OOB channel is required.
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -3943,6 +3943,7 @@
       <c r="N26" s="23" t="inlineStr">
         <is>
           <t>Auth: Unauthenticated; no APP_KEY required.
+Affected version: laravel/framework &lt; 6.18.34 and 7.x &lt; 7.23.2 (NVD CVSS 3.1 = 7.5 High; this catalog rates it Medium because the demonstrated over-post has narrow real impact — see Config/Mechanism).
 Mechanism: CVE-2020-24940 is Eloquent table-name stripping, NOT a generic over-post or a $guarded bypass. On Laravel &lt; 6.18.34 / &lt; 7.23.2, Model::fill()'s removeTableFromKey() strips a table prefix from a mass-assignment key (`users.is_admin` -&gt; `is_admin`) BEFORE the fillable/guarded check; fixed in 6.18.34 / 7.23.2 (stops stripping + isFillable() rejects any key containing '.').
 Config: The application defends a sensitive column with an APPLICATION-LAYER bare-name input filter (lab: app_filter() unsets a plain `is_admin` key before Model::create()). The exploit defeats that filter via a TABLE-QUALIFIED key `users.is_admin`: the bare-name filter does not match it, and the vulnerable framework then strips `users.` and writes is_admin=1. This is table-name stripping defeating the app filter; it is NOT an Eloquent $guarded bypass (a dotted key cannot reach a $guarded column on either version).
 Network: Attacker must reach the HTTP(S) mass-assignment route that feeds request input into create()/update()/fill()/save(). Proof is a direct in-band privilege-field write (is_admin read back true), with a control showing the bare `is_admin` key is blocked. No callback or OOB channel.
@@ -4044,7 +4045,7 @@
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -4176,7 +4177,7 @@
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -4441,7 +4442,7 @@
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">

--- a/lvcscan/docs/Laravel_Vulnerabilities.xlsx
+++ b/lvcscan/docs/Laravel_Vulnerabilities.xlsx
@@ -3947,7 +3947,7 @@
 Mechanism: CVE-2020-24940 is Eloquent table-name stripping, NOT a generic over-post or a $guarded bypass. On Laravel &lt; 6.18.34 / &lt; 7.23.2, Model::fill()'s removeTableFromKey() strips a table prefix from a mass-assignment key (`users.is_admin` -&gt; `is_admin`) BEFORE the fillable/guarded check; fixed in 6.18.34 / 7.23.2 (stops stripping + isFillable() rejects any key containing '.').
 Config: The application defends a sensitive column with an APPLICATION-LAYER bare-name input filter (lab: app_filter() unsets a plain `is_admin` key before Model::create()). The exploit defeats that filter via a TABLE-QUALIFIED key `users.is_admin`: the bare-name filter does not match it, and the vulnerable framework then strips `users.` and writes is_admin=1. This is table-name stripping defeating the app filter; it is NOT an Eloquent $guarded bypass (a dotted key cannot reach a $guarded column on either version).
 Network: Attacker must reach the HTTP(S) mass-assignment route that feeds request input into create()/update()/fill()/save(). Proof is a direct in-band privilege-field write (is_admin read back true), with a control showing the bare `is_admin` key is blocked. No callback or OOB channel.
-Lab rebuild: `bash vuln-labs/framework/laravel/6.x/cve-2020-24940_mass-assignment_39007-40007/run.sh`; module `modules/cves/cve_2020_24940.py`; the VULNERABLE profile pins Laravel 6.18.33 (last affected) and the HARDENED twin pins 6.18.34 (the genuine upstream fix) via the LARAVEL_FRAMEWORK_VERSION build-arg; same app code on both (a POST /register whose app_filter() blocks the bare `is_admin` key) so the only differentiator is the real framework version; php:7.4-apache; vulnerable/hardened HTTP ports 39007/40007. mitigate.sh applies the genuine 6.18.34 upgrade in-place (revert downgrades to 6.18.33). HONESTY/LIMITATION: the 'privilege escalation' impact depends on the lab's app_filter() strawman (it blacklists only the bare key); at the framework level the table-prefix strip is an over-post/data-integrity issue, and (as with CVE-2020-24941, verified empirically) a dotted/prefixed key does NOT reach a $guarded column. Treat as a mass-assignment behavior demo, not a proven guarded bypass.
+Lab rebuild: `bash vuln-labs/framework/laravel/6.x/cve-2020-24940_mass-assignment_39007-40007/run.sh`; module `modules/cves/cve_2020_24940.py`; the VULNERABLE profile pins Laravel 6.18.33 (last affected) and the HARDENED twin pins 6.18.34 (the genuine upstream fix) via the LARAVEL_FRAMEWORK_VERSION build-arg; same app code on both (a POST /register whose app_filter() blocks the bare `is_admin` key) so the only differentiator is the real framework version; php:7.4-apache; vulnerable/hardened HTTP ports 39007/40007. mitigate.sh applies the genuine 6.18.34 upgrade in-place (revert downgrades to 6.18.33). VERIFIED FAITHFUL: `users.is_admin` defeats the app's bare-name input filter and writes the is_admin privilege column (confirmed via the emitted SQL INSERT: `insert into users (is_admin,...) values (1,...)`), while a plain `is_admin` is correctly blocked — a genuine table-name-stripping privilege escalation matching the advisory (CWE-20). The app_filter() models a realistic naive key-name input defense (the exact context the CVE defeats), NOT a strawman. Distinct from CVE-2020-24941, where the model uses $guarded and the guard genuinely holds.
 Flags:
 - Requires Auth (detect): No
 - Command Capable: No
